--- a/outputs/evaluation/architecture/design/v3/CF_M01/run_3/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v3/CF_M01/run_3/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.825</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.8125</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8814</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9876</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.875</v>
       </c>
       <c r="D4" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8771</v>
       </c>
     </row>
@@ -1199,7 +1213,6 @@
       <c r="D2" t="n">
         <v>0.7857</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1220,7 +1233,6 @@
           <t>['AU_06', 'AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_27</t>
@@ -1231,7 +1243,6 @@
           <t>api gateway service, core service, analytical module service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1250,7 +1261,6 @@
           <t>CF_M01_AU01, CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU24</t>
@@ -1281,7 +1291,6 @@
       <c r="D3" t="n">
         <v>0.7887</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1302,7 +1311,6 @@
           <t>['AU_08', 'AU_13', 'AU_05']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_29</t>
@@ -1313,7 +1321,6 @@
           <t>analytical module service, aws, data layer</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1332,7 +1339,6 @@
           <t>CF_M01_AU11, CF_M01_AU15, CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU37</t>
@@ -1363,7 +1369,6 @@
       <c r="D4" t="n">
         <v>0.8309</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1384,7 +1389,6 @@
           <t>['AU_07', 'AU_05', 'AU_13']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_28</t>
@@ -1395,7 +1399,6 @@
           <t>core service, data layer, aws</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1414,7 +1417,6 @@
           <t>CF_M01_AU12, CF_M01_AU16, CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU36</t>
@@ -1470,13 +1472,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -1500,13 +1500,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1552,13 +1550,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Analytical module</t>
@@ -1582,13 +1578,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU12</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1609,7 +1603,6 @@
       <c r="D7" t="n">
         <v>0.9121</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1630,7 +1623,6 @@
           <t>['AU_09', 'AU_24']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_30</t>
@@ -1641,7 +1633,6 @@
           <t>player api service, player</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1660,7 +1651,6 @@
           <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU28</t>
@@ -1691,7 +1681,6 @@
       <c r="D8" t="n">
         <v>0.9135</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1712,7 +1701,6 @@
           <t>['AU_10', 'AU_24']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_31</t>
@@ -1723,7 +1711,6 @@
           <t>web socket service, player</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1742,7 +1729,6 @@
           <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU29</t>
@@ -1798,13 +1784,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -1828,13 +1812,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1855,7 +1837,6 @@
       <c r="D10" t="n">
         <v>0.9499</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1876,7 +1857,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_25</t>
@@ -1887,7 +1867,6 @@
           <t>presentation layer, api gateway service</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1906,7 +1885,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1937,7 +1915,6 @@
       <c r="D11" t="n">
         <v>0.9587</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1958,7 +1935,6 @@
           <t>['AU_06', 'AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_26</t>
@@ -1969,7 +1945,6 @@
           <t>api gateway service, core service, analytical module service</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1988,7 +1963,6 @@
           <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU26</t>
@@ -2044,13 +2018,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>AWS RDS</t>
@@ -2074,13 +2046,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU35</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2126,13 +2096,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2156,13 +2124,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2203,7 +2169,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2214,7 +2179,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -2238,13 +2202,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2290,13 +2252,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2320,13 +2280,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2367,14 +2325,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2393,14 +2348,11 @@
       <c r="P16" t="n">
         <v>8</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU27</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2446,13 +2398,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -2476,13 +2426,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2523,14 +2471,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -2554,13 +2499,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2606,13 +2549,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -2636,13 +2577,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2688,13 +2627,11 @@
           <t>['AU_25']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2718,13 +2655,11 @@
           <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU03</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2770,13 +2705,11 @@
           <t>['AU_06', 'AU_07', 'AU_08', 'AU_09', 'AU_10']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2800,13 +2733,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2847,14 +2778,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2878,13 +2806,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2930,13 +2856,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -2960,13 +2884,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3012,13 +2934,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -3042,13 +2962,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3094,13 +3012,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -3124,13 +3040,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3171,14 +3085,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Business Layer</t>
@@ -3202,13 +3113,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3254,13 +3163,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -3284,13 +3191,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3331,14 +3236,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Server</t>
@@ -3362,13 +3264,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3414,13 +3314,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -3446,13 +3344,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3493,14 +3389,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3519,14 +3412,11 @@
       <c r="P30" t="n">
         <v>41</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3567,14 +3457,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3598,13 +3485,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3645,14 +3530,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Data Layer</t>
@@ -3676,13 +3558,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3728,13 +3608,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3758,13 +3636,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3810,13 +3686,11 @@
           <t>['AU_27']</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3840,13 +3714,11 @@
           <t>CF_M01_AU26</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3920,7 +3792,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Set of cloud computing services used for infrastructure.</t>
@@ -4012,7 +3883,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4048,7 +3918,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4084,7 +3953,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4115,7 +3983,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -4156,7 +4023,6 @@
           <t>SQL database</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -4192,7 +4058,6 @@
           <t>AWS cloud services set</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
@@ -4228,7 +4093,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
